--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_26-08-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_26-08-2025.xlsx
@@ -591,27 +591,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.139); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7defd78d5+2802741]
-	GetHandleVerifier [0x0x7ff7ded3eb70+79568]
-	(No symbol) [0x0x7ff7deadc0fa]
-	(No symbol) [0x0x7ff7deb32a96]
-	(No symbol) [0x0x7ff7deb32d4c]
-	(No symbol) [0x0x7ff7deb86017]
-	(No symbol) [0x0x7ff7deb5accf]
-	(No symbol) [0x0x7ff7deb82e24]
-	(No symbol) [0x0x7ff7deb5aa63]
-	(No symbol) [0x0x7ff7deb23c91]
-	(No symbol) [0x0x7ff7deb24a23]
-	GetHandleVerifier [0x0x7ff7df002ced+2979917]
-	GetHandleVerifier [0x0x7ff7deffd0f3+2956371]
-	GetHandleVerifier [0x0x7ff7df01acbd+3078173]
-	GetHandleVerifier [0x0x7ff7ded5836e+184014]
-	GetHandleVerifier [0x0x7ff7ded6024f+216495]
-	GetHandleVerifier [0x0x7ff7ded470c4+113700]
-	GetHandleVerifier [0x0x7ff7ded47279+114137]
-	GetHandleVerifier [0x0x7ff7ded2df78+10968]
-	BaseThreadInitThunk [0x0x7fffa28de8d7+23]
-	RtlUserThreadStart [0x0x7fffa3edc34c+44]
+	GetHandleVerifier [0x0x7ff62f8278d5+2802741]
+	GetHandleVerifier [0x0x7ff62f58eb70+79568]
+	(No symbol) [0x0x7ff62f32c0fa]
+	(No symbol) [0x0x7ff62f382a96]
+	(No symbol) [0x0x7ff62f382d4c]
+	(No symbol) [0x0x7ff62f3d6017]
+	(No symbol) [0x0x7ff62f3aaccf]
+	(No symbol) [0x0x7ff62f3d2e24]
+	(No symbol) [0x0x7ff62f3aaa63]
+	(No symbol) [0x0x7ff62f373c91]
+	(No symbol) [0x0x7ff62f374a23]
+	GetHandleVerifier [0x0x7ff62f852ced+2979917]
+	GetHandleVerifier [0x0x7ff62f84d0f3+2956371]
+	GetHandleVerifier [0x0x7ff62f86acbd+3078173]
+	GetHandleVerifier [0x0x7ff62f5a836e+184014]
+	GetHandleVerifier [0x0x7ff62f5b024f+216495]
+	GetHandleVerifier [0x0x7ff62f5970c4+113700]
+	GetHandleVerifier [0x0x7ff62f597279+114137]
+	GetHandleVerifier [0x0x7ff62f57df78+10968]
+	BaseThreadInitThunk [0x0x7ffd0f98e8d7+23]
+	RtlUserThreadStart [0x0x7ffd11a3c34c+44]
 </t>
         </is>
       </c>
@@ -712,27 +712,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.139); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7defd78d5+2802741]
-	GetHandleVerifier [0x0x7ff7ded3eb70+79568]
-	(No symbol) [0x0x7ff7deadc0fa]
-	(No symbol) [0x0x7ff7deb32a96]
-	(No symbol) [0x0x7ff7deb32d4c]
-	(No symbol) [0x0x7ff7deb86017]
-	(No symbol) [0x0x7ff7deb5accf]
-	(No symbol) [0x0x7ff7deb82e24]
-	(No symbol) [0x0x7ff7deb5aa63]
-	(No symbol) [0x0x7ff7deb23c91]
-	(No symbol) [0x0x7ff7deb24a23]
-	GetHandleVerifier [0x0x7ff7df002ced+2979917]
-	GetHandleVerifier [0x0x7ff7deffd0f3+2956371]
-	GetHandleVerifier [0x0x7ff7df01acbd+3078173]
-	GetHandleVerifier [0x0x7ff7ded5836e+184014]
-	GetHandleVerifier [0x0x7ff7ded6024f+216495]
-	GetHandleVerifier [0x0x7ff7ded470c4+113700]
-	GetHandleVerifier [0x0x7ff7ded47279+114137]
-	GetHandleVerifier [0x0x7ff7ded2df78+10968]
-	BaseThreadInitThunk [0x0x7fffa28de8d7+23]
-	RtlUserThreadStart [0x0x7fffa3edc34c+44]
+	GetHandleVerifier [0x0x7ff62f8278d5+2802741]
+	GetHandleVerifier [0x0x7ff62f58eb70+79568]
+	(No symbol) [0x0x7ff62f32c0fa]
+	(No symbol) [0x0x7ff62f382a96]
+	(No symbol) [0x0x7ff62f382d4c]
+	(No symbol) [0x0x7ff62f3d6017]
+	(No symbol) [0x0x7ff62f3aaccf]
+	(No symbol) [0x0x7ff62f3d2e24]
+	(No symbol) [0x0x7ff62f3aaa63]
+	(No symbol) [0x0x7ff62f373c91]
+	(No symbol) [0x0x7ff62f374a23]
+	GetHandleVerifier [0x0x7ff62f852ced+2979917]
+	GetHandleVerifier [0x0x7ff62f84d0f3+2956371]
+	GetHandleVerifier [0x0x7ff62f86acbd+3078173]
+	GetHandleVerifier [0x0x7ff62f5a836e+184014]
+	GetHandleVerifier [0x0x7ff62f5b024f+216495]
+	GetHandleVerifier [0x0x7ff62f5970c4+113700]
+	GetHandleVerifier [0x0x7ff62f597279+114137]
+	GetHandleVerifier [0x0x7ff62f57df78+10968]
+	BaseThreadInitThunk [0x0x7ffd0f98e8d7+23]
+	RtlUserThreadStart [0x0x7ffd11a3c34c+44]
 </t>
         </is>
       </c>
@@ -833,27 +833,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.139); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7defd78d5+2802741]
-	GetHandleVerifier [0x0x7ff7ded3eb70+79568]
-	(No symbol) [0x0x7ff7deadc0fa]
-	(No symbol) [0x0x7ff7deb32a96]
-	(No symbol) [0x0x7ff7deb32d4c]
-	(No symbol) [0x0x7ff7deb86017]
-	(No symbol) [0x0x7ff7deb5accf]
-	(No symbol) [0x0x7ff7deb82e24]
-	(No symbol) [0x0x7ff7deb5aa63]
-	(No symbol) [0x0x7ff7deb23c91]
-	(No symbol) [0x0x7ff7deb24a23]
-	GetHandleVerifier [0x0x7ff7df002ced+2979917]
-	GetHandleVerifier [0x0x7ff7deffd0f3+2956371]
-	GetHandleVerifier [0x0x7ff7df01acbd+3078173]
-	GetHandleVerifier [0x0x7ff7ded5836e+184014]
-	GetHandleVerifier [0x0x7ff7ded6024f+216495]
-	GetHandleVerifier [0x0x7ff7ded470c4+113700]
-	GetHandleVerifier [0x0x7ff7ded47279+114137]
-	GetHandleVerifier [0x0x7ff7ded2df78+10968]
-	BaseThreadInitThunk [0x0x7fffa28de8d7+23]
-	RtlUserThreadStart [0x0x7fffa3edc34c+44]
+	GetHandleVerifier [0x0x7ff62f8278d5+2802741]
+	GetHandleVerifier [0x0x7ff62f58eb70+79568]
+	(No symbol) [0x0x7ff62f32c0fa]
+	(No symbol) [0x0x7ff62f382a96]
+	(No symbol) [0x0x7ff62f382d4c]
+	(No symbol) [0x0x7ff62f3d6017]
+	(No symbol) [0x0x7ff62f3aaccf]
+	(No symbol) [0x0x7ff62f3d2e24]
+	(No symbol) [0x0x7ff62f3aaa63]
+	(No symbol) [0x0x7ff62f373c91]
+	(No symbol) [0x0x7ff62f374a23]
+	GetHandleVerifier [0x0x7ff62f852ced+2979917]
+	GetHandleVerifier [0x0x7ff62f84d0f3+2956371]
+	GetHandleVerifier [0x0x7ff62f86acbd+3078173]
+	GetHandleVerifier [0x0x7ff62f5a836e+184014]
+	GetHandleVerifier [0x0x7ff62f5b024f+216495]
+	GetHandleVerifier [0x0x7ff62f5970c4+113700]
+	GetHandleVerifier [0x0x7ff62f597279+114137]
+	GetHandleVerifier [0x0x7ff62f57df78+10968]
+	BaseThreadInitThunk [0x0x7ffd0f98e8d7+23]
+	RtlUserThreadStart [0x0x7ffd11a3c34c+44]
 </t>
         </is>
       </c>
@@ -954,27 +954,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.139); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7defd78d5+2802741]
-	GetHandleVerifier [0x0x7ff7ded3eb70+79568]
-	(No symbol) [0x0x7ff7deadc0fa]
-	(No symbol) [0x0x7ff7deb32a96]
-	(No symbol) [0x0x7ff7deb32d4c]
-	(No symbol) [0x0x7ff7deb86017]
-	(No symbol) [0x0x7ff7deb5accf]
-	(No symbol) [0x0x7ff7deb82e24]
-	(No symbol) [0x0x7ff7deb5aa63]
-	(No symbol) [0x0x7ff7deb23c91]
-	(No symbol) [0x0x7ff7deb24a23]
-	GetHandleVerifier [0x0x7ff7df002ced+2979917]
-	GetHandleVerifier [0x0x7ff7deffd0f3+2956371]
-	GetHandleVerifier [0x0x7ff7df01acbd+3078173]
-	GetHandleVerifier [0x0x7ff7ded5836e+184014]
-	GetHandleVerifier [0x0x7ff7ded6024f+216495]
-	GetHandleVerifier [0x0x7ff7ded470c4+113700]
-	GetHandleVerifier [0x0x7ff7ded47279+114137]
-	GetHandleVerifier [0x0x7ff7ded2df78+10968]
-	BaseThreadInitThunk [0x0x7fffa28de8d7+23]
-	RtlUserThreadStart [0x0x7fffa3edc34c+44]
+	GetHandleVerifier [0x0x7ff62f8278d5+2802741]
+	GetHandleVerifier [0x0x7ff62f58eb70+79568]
+	(No symbol) [0x0x7ff62f32c0fa]
+	(No symbol) [0x0x7ff62f382a96]
+	(No symbol) [0x0x7ff62f382d4c]
+	(No symbol) [0x0x7ff62f3d6017]
+	(No symbol) [0x0x7ff62f3aaccf]
+	(No symbol) [0x0x7ff62f3d2e24]
+	(No symbol) [0x0x7ff62f3aaa63]
+	(No symbol) [0x0x7ff62f373c91]
+	(No symbol) [0x0x7ff62f374a23]
+	GetHandleVerifier [0x0x7ff62f852ced+2979917]
+	GetHandleVerifier [0x0x7ff62f84d0f3+2956371]
+	GetHandleVerifier [0x0x7ff62f86acbd+3078173]
+	GetHandleVerifier [0x0x7ff62f5a836e+184014]
+	GetHandleVerifier [0x0x7ff62f5b024f+216495]
+	GetHandleVerifier [0x0x7ff62f5970c4+113700]
+	GetHandleVerifier [0x0x7ff62f597279+114137]
+	GetHandleVerifier [0x0x7ff62f57df78+10968]
+	BaseThreadInitThunk [0x0x7ffd0f98e8d7+23]
+	RtlUserThreadStart [0x0x7ffd11a3c34c+44]
 </t>
         </is>
       </c>
@@ -1075,27 +1075,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.139); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7defd78d5+2802741]
-	GetHandleVerifier [0x0x7ff7ded3eb70+79568]
-	(No symbol) [0x0x7ff7deadc0fa]
-	(No symbol) [0x0x7ff7deb32a96]
-	(No symbol) [0x0x7ff7deb32d4c]
-	(No symbol) [0x0x7ff7deb86017]
-	(No symbol) [0x0x7ff7deb5accf]
-	(No symbol) [0x0x7ff7deb82e24]
-	(No symbol) [0x0x7ff7deb5aa63]
-	(No symbol) [0x0x7ff7deb23c91]
-	(No symbol) [0x0x7ff7deb24a23]
-	GetHandleVerifier [0x0x7ff7df002ced+2979917]
-	GetHandleVerifier [0x0x7ff7deffd0f3+2956371]
-	GetHandleVerifier [0x0x7ff7df01acbd+3078173]
-	GetHandleVerifier [0x0x7ff7ded5836e+184014]
-	GetHandleVerifier [0x0x7ff7ded6024f+216495]
-	GetHandleVerifier [0x0x7ff7ded470c4+113700]
-	GetHandleVerifier [0x0x7ff7ded47279+114137]
-	GetHandleVerifier [0x0x7ff7ded2df78+10968]
-	BaseThreadInitThunk [0x0x7fffa28de8d7+23]
-	RtlUserThreadStart [0x0x7fffa3edc34c+44]
+	GetHandleVerifier [0x0x7ff62f8278d5+2802741]
+	GetHandleVerifier [0x0x7ff62f58eb70+79568]
+	(No symbol) [0x0x7ff62f32c0fa]
+	(No symbol) [0x0x7ff62f382a96]
+	(No symbol) [0x0x7ff62f382d4c]
+	(No symbol) [0x0x7ff62f3d6017]
+	(No symbol) [0x0x7ff62f3aaccf]
+	(No symbol) [0x0x7ff62f3d2e24]
+	(No symbol) [0x0x7ff62f3aaa63]
+	(No symbol) [0x0x7ff62f373c91]
+	(No symbol) [0x0x7ff62f374a23]
+	GetHandleVerifier [0x0x7ff62f852ced+2979917]
+	GetHandleVerifier [0x0x7ff62f84d0f3+2956371]
+	GetHandleVerifier [0x0x7ff62f86acbd+3078173]
+	GetHandleVerifier [0x0x7ff62f5a836e+184014]
+	GetHandleVerifier [0x0x7ff62f5b024f+216495]
+	GetHandleVerifier [0x0x7ff62f5970c4+113700]
+	GetHandleVerifier [0x0x7ff62f597279+114137]
+	GetHandleVerifier [0x0x7ff62f57df78+10968]
+	BaseThreadInitThunk [0x0x7ffd0f98e8d7+23]
+	RtlUserThreadStart [0x0x7ffd11a3c34c+44]
 </t>
         </is>
       </c>
@@ -1196,27 +1196,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.139); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7defd78d5+2802741]
-	GetHandleVerifier [0x0x7ff7ded3eb70+79568]
-	(No symbol) [0x0x7ff7deadc0fa]
-	(No symbol) [0x0x7ff7deb32a96]
-	(No symbol) [0x0x7ff7deb32d4c]
-	(No symbol) [0x0x7ff7deb86017]
-	(No symbol) [0x0x7ff7deb5accf]
-	(No symbol) [0x0x7ff7deb82e24]
-	(No symbol) [0x0x7ff7deb5aa63]
-	(No symbol) [0x0x7ff7deb23c91]
-	(No symbol) [0x0x7ff7deb24a23]
-	GetHandleVerifier [0x0x7ff7df002ced+2979917]
-	GetHandleVerifier [0x0x7ff7deffd0f3+2956371]
-	GetHandleVerifier [0x0x7ff7df01acbd+3078173]
-	GetHandleVerifier [0x0x7ff7ded5836e+184014]
-	GetHandleVerifier [0x0x7ff7ded6024f+216495]
-	GetHandleVerifier [0x0x7ff7ded470c4+113700]
-	GetHandleVerifier [0x0x7ff7ded47279+114137]
-	GetHandleVerifier [0x0x7ff7ded2df78+10968]
-	BaseThreadInitThunk [0x0x7fffa28de8d7+23]
-	RtlUserThreadStart [0x0x7fffa3edc34c+44]
+	GetHandleVerifier [0x0x7ff62f8278d5+2802741]
+	GetHandleVerifier [0x0x7ff62f58eb70+79568]
+	(No symbol) [0x0x7ff62f32c0fa]
+	(No symbol) [0x0x7ff62f382a96]
+	(No symbol) [0x0x7ff62f382d4c]
+	(No symbol) [0x0x7ff62f3d6017]
+	(No symbol) [0x0x7ff62f3aaccf]
+	(No symbol) [0x0x7ff62f3d2e24]
+	(No symbol) [0x0x7ff62f3aaa63]
+	(No symbol) [0x0x7ff62f373c91]
+	(No symbol) [0x0x7ff62f374a23]
+	GetHandleVerifier [0x0x7ff62f852ced+2979917]
+	GetHandleVerifier [0x0x7ff62f84d0f3+2956371]
+	GetHandleVerifier [0x0x7ff62f86acbd+3078173]
+	GetHandleVerifier [0x0x7ff62f5a836e+184014]
+	GetHandleVerifier [0x0x7ff62f5b024f+216495]
+	GetHandleVerifier [0x0x7ff62f5970c4+113700]
+	GetHandleVerifier [0x0x7ff62f597279+114137]
+	GetHandleVerifier [0x0x7ff62f57df78+10968]
+	BaseThreadInitThunk [0x0x7ffd0f98e8d7+23]
+	RtlUserThreadStart [0x0x7ffd11a3c34c+44]
 </t>
         </is>
       </c>
@@ -1317,27 +1317,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.139); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7defd78d5+2802741]
-	GetHandleVerifier [0x0x7ff7ded3eb70+79568]
-	(No symbol) [0x0x7ff7deadc0fa]
-	(No symbol) [0x0x7ff7deb32a96]
-	(No symbol) [0x0x7ff7deb32d4c]
-	(No symbol) [0x0x7ff7deb86017]
-	(No symbol) [0x0x7ff7deb5accf]
-	(No symbol) [0x0x7ff7deb82e24]
-	(No symbol) [0x0x7ff7deb5aa63]
-	(No symbol) [0x0x7ff7deb23c91]
-	(No symbol) [0x0x7ff7deb24a23]
-	GetHandleVerifier [0x0x7ff7df002ced+2979917]
-	GetHandleVerifier [0x0x7ff7deffd0f3+2956371]
-	GetHandleVerifier [0x0x7ff7df01acbd+3078173]
-	GetHandleVerifier [0x0x7ff7ded5836e+184014]
-	GetHandleVerifier [0x0x7ff7ded6024f+216495]
-	GetHandleVerifier [0x0x7ff7ded470c4+113700]
-	GetHandleVerifier [0x0x7ff7ded47279+114137]
-	GetHandleVerifier [0x0x7ff7ded2df78+10968]
-	BaseThreadInitThunk [0x0x7fffa28de8d7+23]
-	RtlUserThreadStart [0x0x7fffa3edc34c+44]
+	GetHandleVerifier [0x0x7ff62f8278d5+2802741]
+	GetHandleVerifier [0x0x7ff62f58eb70+79568]
+	(No symbol) [0x0x7ff62f32c0fa]
+	(No symbol) [0x0x7ff62f382a96]
+	(No symbol) [0x0x7ff62f382d4c]
+	(No symbol) [0x0x7ff62f3d6017]
+	(No symbol) [0x0x7ff62f3aaccf]
+	(No symbol) [0x0x7ff62f3d2e24]
+	(No symbol) [0x0x7ff62f3aaa63]
+	(No symbol) [0x0x7ff62f373c91]
+	(No symbol) [0x0x7ff62f374a23]
+	GetHandleVerifier [0x0x7ff62f852ced+2979917]
+	GetHandleVerifier [0x0x7ff62f84d0f3+2956371]
+	GetHandleVerifier [0x0x7ff62f86acbd+3078173]
+	GetHandleVerifier [0x0x7ff62f5a836e+184014]
+	GetHandleVerifier [0x0x7ff62f5b024f+216495]
+	GetHandleVerifier [0x0x7ff62f5970c4+113700]
+	GetHandleVerifier [0x0x7ff62f597279+114137]
+	GetHandleVerifier [0x0x7ff62f57df78+10968]
+	BaseThreadInitThunk [0x0x7ffd0f98e8d7+23]
+	RtlUserThreadStart [0x0x7ffd11a3c34c+44]
 </t>
         </is>
       </c>
@@ -1438,27 +1438,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.139); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7defd78d5+2802741]
-	GetHandleVerifier [0x0x7ff7ded3eb70+79568]
-	(No symbol) [0x0x7ff7deadc0fa]
-	(No symbol) [0x0x7ff7deb32a96]
-	(No symbol) [0x0x7ff7deb32d4c]
-	(No symbol) [0x0x7ff7deb86017]
-	(No symbol) [0x0x7ff7deb5accf]
-	(No symbol) [0x0x7ff7deb82e24]
-	(No symbol) [0x0x7ff7deb5aa63]
-	(No symbol) [0x0x7ff7deb23c91]
-	(No symbol) [0x0x7ff7deb24a23]
-	GetHandleVerifier [0x0x7ff7df002ced+2979917]
-	GetHandleVerifier [0x0x7ff7deffd0f3+2956371]
-	GetHandleVerifier [0x0x7ff7df01acbd+3078173]
-	GetHandleVerifier [0x0x7ff7ded5836e+184014]
-	GetHandleVerifier [0x0x7ff7ded6024f+216495]
-	GetHandleVerifier [0x0x7ff7ded470c4+113700]
-	GetHandleVerifier [0x0x7ff7ded47279+114137]
-	GetHandleVerifier [0x0x7ff7ded2df78+10968]
-	BaseThreadInitThunk [0x0x7fffa28de8d7+23]
-	RtlUserThreadStart [0x0x7fffa3edc34c+44]
+	GetHandleVerifier [0x0x7ff62f8278d5+2802741]
+	GetHandleVerifier [0x0x7ff62f58eb70+79568]
+	(No symbol) [0x0x7ff62f32c0fa]
+	(No symbol) [0x0x7ff62f382a96]
+	(No symbol) [0x0x7ff62f382d4c]
+	(No symbol) [0x0x7ff62f3d6017]
+	(No symbol) [0x0x7ff62f3aaccf]
+	(No symbol) [0x0x7ff62f3d2e24]
+	(No symbol) [0x0x7ff62f3aaa63]
+	(No symbol) [0x0x7ff62f373c91]
+	(No symbol) [0x0x7ff62f374a23]
+	GetHandleVerifier [0x0x7ff62f852ced+2979917]
+	GetHandleVerifier [0x0x7ff62f84d0f3+2956371]
+	GetHandleVerifier [0x0x7ff62f86acbd+3078173]
+	GetHandleVerifier [0x0x7ff62f5a836e+184014]
+	GetHandleVerifier [0x0x7ff62f5b024f+216495]
+	GetHandleVerifier [0x0x7ff62f5970c4+113700]
+	GetHandleVerifier [0x0x7ff62f597279+114137]
+	GetHandleVerifier [0x0x7ff62f57df78+10968]
+	BaseThreadInitThunk [0x0x7ffd0f98e8d7+23]
+	RtlUserThreadStart [0x0x7ffd11a3c34c+44]
 </t>
         </is>
       </c>
@@ -1559,27 +1559,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.139); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7defd78d5+2802741]
-	GetHandleVerifier [0x0x7ff7ded3eb70+79568]
-	(No symbol) [0x0x7ff7deadc0fa]
-	(No symbol) [0x0x7ff7deb32a96]
-	(No symbol) [0x0x7ff7deb32d4c]
-	(No symbol) [0x0x7ff7deb86017]
-	(No symbol) [0x0x7ff7deb5accf]
-	(No symbol) [0x0x7ff7deb82e24]
-	(No symbol) [0x0x7ff7deb5aa63]
-	(No symbol) [0x0x7ff7deb23c91]
-	(No symbol) [0x0x7ff7deb24a23]
-	GetHandleVerifier [0x0x7ff7df002ced+2979917]
-	GetHandleVerifier [0x0x7ff7deffd0f3+2956371]
-	GetHandleVerifier [0x0x7ff7df01acbd+3078173]
-	GetHandleVerifier [0x0x7ff7ded5836e+184014]
-	GetHandleVerifier [0x0x7ff7ded6024f+216495]
-	GetHandleVerifier [0x0x7ff7ded470c4+113700]
-	GetHandleVerifier [0x0x7ff7ded47279+114137]
-	GetHandleVerifier [0x0x7ff7ded2df78+10968]
-	BaseThreadInitThunk [0x0x7fffa28de8d7+23]
-	RtlUserThreadStart [0x0x7fffa3edc34c+44]
+	GetHandleVerifier [0x0x7ff62f8278d5+2802741]
+	GetHandleVerifier [0x0x7ff62f58eb70+79568]
+	(No symbol) [0x0x7ff62f32c0fa]
+	(No symbol) [0x0x7ff62f382a96]
+	(No symbol) [0x0x7ff62f382d4c]
+	(No symbol) [0x0x7ff62f3d6017]
+	(No symbol) [0x0x7ff62f3aaccf]
+	(No symbol) [0x0x7ff62f3d2e24]
+	(No symbol) [0x0x7ff62f3aaa63]
+	(No symbol) [0x0x7ff62f373c91]
+	(No symbol) [0x0x7ff62f374a23]
+	GetHandleVerifier [0x0x7ff62f852ced+2979917]
+	GetHandleVerifier [0x0x7ff62f84d0f3+2956371]
+	GetHandleVerifier [0x0x7ff62f86acbd+3078173]
+	GetHandleVerifier [0x0x7ff62f5a836e+184014]
+	GetHandleVerifier [0x0x7ff62f5b024f+216495]
+	GetHandleVerifier [0x0x7ff62f5970c4+113700]
+	GetHandleVerifier [0x0x7ff62f597279+114137]
+	GetHandleVerifier [0x0x7ff62f57df78+10968]
+	BaseThreadInitThunk [0x0x7ffd0f98e8d7+23]
+	RtlUserThreadStart [0x0x7ffd11a3c34c+44]
 </t>
         </is>
       </c>
@@ -1657,7 +1657,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>£31.00</t>
+          <t>Error: 'NoneType' object has no attribute 'find'</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1680,27 +1680,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.139); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7defd78d5+2802741]
-	GetHandleVerifier [0x0x7ff7ded3eb70+79568]
-	(No symbol) [0x0x7ff7deadc0fa]
-	(No symbol) [0x0x7ff7deb32a96]
-	(No symbol) [0x0x7ff7deb32d4c]
-	(No symbol) [0x0x7ff7deb86017]
-	(No symbol) [0x0x7ff7deb5accf]
-	(No symbol) [0x0x7ff7deb82e24]
-	(No symbol) [0x0x7ff7deb5aa63]
-	(No symbol) [0x0x7ff7deb23c91]
-	(No symbol) [0x0x7ff7deb24a23]
-	GetHandleVerifier [0x0x7ff7df002ced+2979917]
-	GetHandleVerifier [0x0x7ff7deffd0f3+2956371]
-	GetHandleVerifier [0x0x7ff7df01acbd+3078173]
-	GetHandleVerifier [0x0x7ff7ded5836e+184014]
-	GetHandleVerifier [0x0x7ff7ded6024f+216495]
-	GetHandleVerifier [0x0x7ff7ded470c4+113700]
-	GetHandleVerifier [0x0x7ff7ded47279+114137]
-	GetHandleVerifier [0x0x7ff7ded2df78+10968]
-	BaseThreadInitThunk [0x0x7fffa28de8d7+23]
-	RtlUserThreadStart [0x0x7fffa3edc34c+44]
+	GetHandleVerifier [0x0x7ff62f8278d5+2802741]
+	GetHandleVerifier [0x0x7ff62f58eb70+79568]
+	(No symbol) [0x0x7ff62f32c0fa]
+	(No symbol) [0x0x7ff62f382a96]
+	(No symbol) [0x0x7ff62f382d4c]
+	(No symbol) [0x0x7ff62f3d6017]
+	(No symbol) [0x0x7ff62f3aaccf]
+	(No symbol) [0x0x7ff62f3d2e24]
+	(No symbol) [0x0x7ff62f3aaa63]
+	(No symbol) [0x0x7ff62f373c91]
+	(No symbol) [0x0x7ff62f374a23]
+	GetHandleVerifier [0x0x7ff62f852ced+2979917]
+	GetHandleVerifier [0x0x7ff62f84d0f3+2956371]
+	GetHandleVerifier [0x0x7ff62f86acbd+3078173]
+	GetHandleVerifier [0x0x7ff62f5a836e+184014]
+	GetHandleVerifier [0x0x7ff62f5b024f+216495]
+	GetHandleVerifier [0x0x7ff62f5970c4+113700]
+	GetHandleVerifier [0x0x7ff62f597279+114137]
+	GetHandleVerifier [0x0x7ff62f57df78+10968]
+	BaseThreadInitThunk [0x0x7ffd0f98e8d7+23]
+	RtlUserThreadStart [0x0x7ffd11a3c34c+44]
 </t>
         </is>
       </c>
@@ -1801,27 +1801,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.139); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7defd78d5+2802741]
-	GetHandleVerifier [0x0x7ff7ded3eb70+79568]
-	(No symbol) [0x0x7ff7deadc0fa]
-	(No symbol) [0x0x7ff7deb32a96]
-	(No symbol) [0x0x7ff7deb32d4c]
-	(No symbol) [0x0x7ff7deb86017]
-	(No symbol) [0x0x7ff7deb5accf]
-	(No symbol) [0x0x7ff7deb82e24]
-	(No symbol) [0x0x7ff7deb5aa63]
-	(No symbol) [0x0x7ff7deb23c91]
-	(No symbol) [0x0x7ff7deb24a23]
-	GetHandleVerifier [0x0x7ff7df002ced+2979917]
-	GetHandleVerifier [0x0x7ff7deffd0f3+2956371]
-	GetHandleVerifier [0x0x7ff7df01acbd+3078173]
-	GetHandleVerifier [0x0x7ff7ded5836e+184014]
-	GetHandleVerifier [0x0x7ff7ded6024f+216495]
-	GetHandleVerifier [0x0x7ff7ded470c4+113700]
-	GetHandleVerifier [0x0x7ff7ded47279+114137]
-	GetHandleVerifier [0x0x7ff7ded2df78+10968]
-	BaseThreadInitThunk [0x0x7fffa28de8d7+23]
-	RtlUserThreadStart [0x0x7fffa3edc34c+44]
+	GetHandleVerifier [0x0x7ff62f8278d5+2802741]
+	GetHandleVerifier [0x0x7ff62f58eb70+79568]
+	(No symbol) [0x0x7ff62f32c0fa]
+	(No symbol) [0x0x7ff62f382a96]
+	(No symbol) [0x0x7ff62f382d4c]
+	(No symbol) [0x0x7ff62f3d6017]
+	(No symbol) [0x0x7ff62f3aaccf]
+	(No symbol) [0x0x7ff62f3d2e24]
+	(No symbol) [0x0x7ff62f3aaa63]
+	(No symbol) [0x0x7ff62f373c91]
+	(No symbol) [0x0x7ff62f374a23]
+	GetHandleVerifier [0x0x7ff62f852ced+2979917]
+	GetHandleVerifier [0x0x7ff62f84d0f3+2956371]
+	GetHandleVerifier [0x0x7ff62f86acbd+3078173]
+	GetHandleVerifier [0x0x7ff62f5a836e+184014]
+	GetHandleVerifier [0x0x7ff62f5b024f+216495]
+	GetHandleVerifier [0x0x7ff62f5970c4+113700]
+	GetHandleVerifier [0x0x7ff62f597279+114137]
+	GetHandleVerifier [0x0x7ff62f57df78+10968]
+	BaseThreadInitThunk [0x0x7ffd0f98e8d7+23]
+	RtlUserThreadStart [0x0x7ffd11a3c34c+44]
 </t>
         </is>
       </c>
@@ -1899,7 +1899,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>£38.00</t>
+          <t>Error: 'NoneType' object has no attribute 'find'</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1922,27 +1922,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.139); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7defd78d5+2802741]
-	GetHandleVerifier [0x0x7ff7ded3eb70+79568]
-	(No symbol) [0x0x7ff7deadc0fa]
-	(No symbol) [0x0x7ff7deb32a96]
-	(No symbol) [0x0x7ff7deb32d4c]
-	(No symbol) [0x0x7ff7deb86017]
-	(No symbol) [0x0x7ff7deb5accf]
-	(No symbol) [0x0x7ff7deb82e24]
-	(No symbol) [0x0x7ff7deb5aa63]
-	(No symbol) [0x0x7ff7deb23c91]
-	(No symbol) [0x0x7ff7deb24a23]
-	GetHandleVerifier [0x0x7ff7df002ced+2979917]
-	GetHandleVerifier [0x0x7ff7deffd0f3+2956371]
-	GetHandleVerifier [0x0x7ff7df01acbd+3078173]
-	GetHandleVerifier [0x0x7ff7ded5836e+184014]
-	GetHandleVerifier [0x0x7ff7ded6024f+216495]
-	GetHandleVerifier [0x0x7ff7ded470c4+113700]
-	GetHandleVerifier [0x0x7ff7ded47279+114137]
-	GetHandleVerifier [0x0x7ff7ded2df78+10968]
-	BaseThreadInitThunk [0x0x7fffa28de8d7+23]
-	RtlUserThreadStart [0x0x7fffa3edc34c+44]
+	GetHandleVerifier [0x0x7ff62f8278d5+2802741]
+	GetHandleVerifier [0x0x7ff62f58eb70+79568]
+	(No symbol) [0x0x7ff62f32c0fa]
+	(No symbol) [0x0x7ff62f382a96]
+	(No symbol) [0x0x7ff62f382d4c]
+	(No symbol) [0x0x7ff62f3d6017]
+	(No symbol) [0x0x7ff62f3aaccf]
+	(No symbol) [0x0x7ff62f3d2e24]
+	(No symbol) [0x0x7ff62f3aaa63]
+	(No symbol) [0x0x7ff62f373c91]
+	(No symbol) [0x0x7ff62f374a23]
+	GetHandleVerifier [0x0x7ff62f852ced+2979917]
+	GetHandleVerifier [0x0x7ff62f84d0f3+2956371]
+	GetHandleVerifier [0x0x7ff62f86acbd+3078173]
+	GetHandleVerifier [0x0x7ff62f5a836e+184014]
+	GetHandleVerifier [0x0x7ff62f5b024f+216495]
+	GetHandleVerifier [0x0x7ff62f5970c4+113700]
+	GetHandleVerifier [0x0x7ff62f597279+114137]
+	GetHandleVerifier [0x0x7ff62f57df78+10968]
+	BaseThreadInitThunk [0x0x7ffd0f98e8d7+23]
+	RtlUserThreadStart [0x0x7ffd11a3c34c+44]
 </t>
         </is>
       </c>
@@ -2020,7 +2020,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>£46.00</t>
+          <t>Error: 'NoneType' object has no attribute 'find'</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2043,27 +2043,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.139); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7defd78d5+2802741]
-	GetHandleVerifier [0x0x7ff7ded3eb70+79568]
-	(No symbol) [0x0x7ff7deadc0fa]
-	(No symbol) [0x0x7ff7deb32a96]
-	(No symbol) [0x0x7ff7deb32d4c]
-	(No symbol) [0x0x7ff7deb86017]
-	(No symbol) [0x0x7ff7deb5accf]
-	(No symbol) [0x0x7ff7deb82e24]
-	(No symbol) [0x0x7ff7deb5aa63]
-	(No symbol) [0x0x7ff7deb23c91]
-	(No symbol) [0x0x7ff7deb24a23]
-	GetHandleVerifier [0x0x7ff7df002ced+2979917]
-	GetHandleVerifier [0x0x7ff7deffd0f3+2956371]
-	GetHandleVerifier [0x0x7ff7df01acbd+3078173]
-	GetHandleVerifier [0x0x7ff7ded5836e+184014]
-	GetHandleVerifier [0x0x7ff7ded6024f+216495]
-	GetHandleVerifier [0x0x7ff7ded470c4+113700]
-	GetHandleVerifier [0x0x7ff7ded47279+114137]
-	GetHandleVerifier [0x0x7ff7ded2df78+10968]
-	BaseThreadInitThunk [0x0x7fffa28de8d7+23]
-	RtlUserThreadStart [0x0x7fffa3edc34c+44]
+	GetHandleVerifier [0x0x7ff62f8278d5+2802741]
+	GetHandleVerifier [0x0x7ff62f58eb70+79568]
+	(No symbol) [0x0x7ff62f32c0fa]
+	(No symbol) [0x0x7ff62f382a96]
+	(No symbol) [0x0x7ff62f382d4c]
+	(No symbol) [0x0x7ff62f3d6017]
+	(No symbol) [0x0x7ff62f3aaccf]
+	(No symbol) [0x0x7ff62f3d2e24]
+	(No symbol) [0x0x7ff62f3aaa63]
+	(No symbol) [0x0x7ff62f373c91]
+	(No symbol) [0x0x7ff62f374a23]
+	GetHandleVerifier [0x0x7ff62f852ced+2979917]
+	GetHandleVerifier [0x0x7ff62f84d0f3+2956371]
+	GetHandleVerifier [0x0x7ff62f86acbd+3078173]
+	GetHandleVerifier [0x0x7ff62f5a836e+184014]
+	GetHandleVerifier [0x0x7ff62f5b024f+216495]
+	GetHandleVerifier [0x0x7ff62f5970c4+113700]
+	GetHandleVerifier [0x0x7ff62f597279+114137]
+	GetHandleVerifier [0x0x7ff62f57df78+10968]
+	BaseThreadInitThunk [0x0x7ffd0f98e8d7+23]
+	RtlUserThreadStart [0x0x7ffd11a3c34c+44]
 </t>
         </is>
       </c>
@@ -2164,27 +2164,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.139); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7defd78d5+2802741]
-	GetHandleVerifier [0x0x7ff7ded3eb70+79568]
-	(No symbol) [0x0x7ff7deadc0fa]
-	(No symbol) [0x0x7ff7deb32a96]
-	(No symbol) [0x0x7ff7deb32d4c]
-	(No symbol) [0x0x7ff7deb86017]
-	(No symbol) [0x0x7ff7deb5accf]
-	(No symbol) [0x0x7ff7deb82e24]
-	(No symbol) [0x0x7ff7deb5aa63]
-	(No symbol) [0x0x7ff7deb23c91]
-	(No symbol) [0x0x7ff7deb24a23]
-	GetHandleVerifier [0x0x7ff7df002ced+2979917]
-	GetHandleVerifier [0x0x7ff7deffd0f3+2956371]
-	GetHandleVerifier [0x0x7ff7df01acbd+3078173]
-	GetHandleVerifier [0x0x7ff7ded5836e+184014]
-	GetHandleVerifier [0x0x7ff7ded6024f+216495]
-	GetHandleVerifier [0x0x7ff7ded470c4+113700]
-	GetHandleVerifier [0x0x7ff7ded47279+114137]
-	GetHandleVerifier [0x0x7ff7ded2df78+10968]
-	BaseThreadInitThunk [0x0x7fffa28de8d7+23]
-	RtlUserThreadStart [0x0x7fffa3edc34c+44]
+	GetHandleVerifier [0x0x7ff62f8278d5+2802741]
+	GetHandleVerifier [0x0x7ff62f58eb70+79568]
+	(No symbol) [0x0x7ff62f32c0fa]
+	(No symbol) [0x0x7ff62f382a96]
+	(No symbol) [0x0x7ff62f382d4c]
+	(No symbol) [0x0x7ff62f3d6017]
+	(No symbol) [0x0x7ff62f3aaccf]
+	(No symbol) [0x0x7ff62f3d2e24]
+	(No symbol) [0x0x7ff62f3aaa63]
+	(No symbol) [0x0x7ff62f373c91]
+	(No symbol) [0x0x7ff62f374a23]
+	GetHandleVerifier [0x0x7ff62f852ced+2979917]
+	GetHandleVerifier [0x0x7ff62f84d0f3+2956371]
+	GetHandleVerifier [0x0x7ff62f86acbd+3078173]
+	GetHandleVerifier [0x0x7ff62f5a836e+184014]
+	GetHandleVerifier [0x0x7ff62f5b024f+216495]
+	GetHandleVerifier [0x0x7ff62f5970c4+113700]
+	GetHandleVerifier [0x0x7ff62f597279+114137]
+	GetHandleVerifier [0x0x7ff62f57df78+10968]
+	BaseThreadInitThunk [0x0x7ffd0f98e8d7+23]
+	RtlUserThreadStart [0x0x7ffd11a3c34c+44]
 </t>
         </is>
       </c>
@@ -2285,27 +2285,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.139); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7defd78d5+2802741]
-	GetHandleVerifier [0x0x7ff7ded3eb70+79568]
-	(No symbol) [0x0x7ff7deadc0fa]
-	(No symbol) [0x0x7ff7deb32a96]
-	(No symbol) [0x0x7ff7deb32d4c]
-	(No symbol) [0x0x7ff7deb86017]
-	(No symbol) [0x0x7ff7deb5accf]
-	(No symbol) [0x0x7ff7deb82e24]
-	(No symbol) [0x0x7ff7deb5aa63]
-	(No symbol) [0x0x7ff7deb23c91]
-	(No symbol) [0x0x7ff7deb24a23]
-	GetHandleVerifier [0x0x7ff7df002ced+2979917]
-	GetHandleVerifier [0x0x7ff7deffd0f3+2956371]
-	GetHandleVerifier [0x0x7ff7df01acbd+3078173]
-	GetHandleVerifier [0x0x7ff7ded5836e+184014]
-	GetHandleVerifier [0x0x7ff7ded6024f+216495]
-	GetHandleVerifier [0x0x7ff7ded470c4+113700]
-	GetHandleVerifier [0x0x7ff7ded47279+114137]
-	GetHandleVerifier [0x0x7ff7ded2df78+10968]
-	BaseThreadInitThunk [0x0x7fffa28de8d7+23]
-	RtlUserThreadStart [0x0x7fffa3edc34c+44]
+	GetHandleVerifier [0x0x7ff62f8278d5+2802741]
+	GetHandleVerifier [0x0x7ff62f58eb70+79568]
+	(No symbol) [0x0x7ff62f32c0fa]
+	(No symbol) [0x0x7ff62f382a96]
+	(No symbol) [0x0x7ff62f382d4c]
+	(No symbol) [0x0x7ff62f3d6017]
+	(No symbol) [0x0x7ff62f3aaccf]
+	(No symbol) [0x0x7ff62f3d2e24]
+	(No symbol) [0x0x7ff62f3aaa63]
+	(No symbol) [0x0x7ff62f373c91]
+	(No symbol) [0x0x7ff62f374a23]
+	GetHandleVerifier [0x0x7ff62f852ced+2979917]
+	GetHandleVerifier [0x0x7ff62f84d0f3+2956371]
+	GetHandleVerifier [0x0x7ff62f86acbd+3078173]
+	GetHandleVerifier [0x0x7ff62f5a836e+184014]
+	GetHandleVerifier [0x0x7ff62f5b024f+216495]
+	GetHandleVerifier [0x0x7ff62f5970c4+113700]
+	GetHandleVerifier [0x0x7ff62f597279+114137]
+	GetHandleVerifier [0x0x7ff62f57df78+10968]
+	BaseThreadInitThunk [0x0x7ffd0f98e8d7+23]
+	RtlUserThreadStart [0x0x7ffd11a3c34c+44]
 </t>
         </is>
       </c>
@@ -2503,27 +2503,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.139); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7defd78d5+2802741]
-	GetHandleVerifier [0x0x7ff7ded3eb70+79568]
-	(No symbol) [0x0x7ff7deadc0fa]
-	(No symbol) [0x0x7ff7deb32a96]
-	(No symbol) [0x0x7ff7deb32d4c]
-	(No symbol) [0x0x7ff7deb86017]
-	(No symbol) [0x0x7ff7deb5accf]
-	(No symbol) [0x0x7ff7deb82e24]
-	(No symbol) [0x0x7ff7deb5aa63]
-	(No symbol) [0x0x7ff7deb23c91]
-	(No symbol) [0x0x7ff7deb24a23]
-	GetHandleVerifier [0x0x7ff7df002ced+2979917]
-	GetHandleVerifier [0x0x7ff7deffd0f3+2956371]
-	GetHandleVerifier [0x0x7ff7df01acbd+3078173]
-	GetHandleVerifier [0x0x7ff7ded5836e+184014]
-	GetHandleVerifier [0x0x7ff7ded6024f+216495]
-	GetHandleVerifier [0x0x7ff7ded470c4+113700]
-	GetHandleVerifier [0x0x7ff7ded47279+114137]
-	GetHandleVerifier [0x0x7ff7ded2df78+10968]
-	BaseThreadInitThunk [0x0x7fffa28de8d7+23]
-	RtlUserThreadStart [0x0x7fffa3edc34c+44]
+	GetHandleVerifier [0x0x7ff62f8278d5+2802741]
+	GetHandleVerifier [0x0x7ff62f58eb70+79568]
+	(No symbol) [0x0x7ff62f32c0fa]
+	(No symbol) [0x0x7ff62f382a96]
+	(No symbol) [0x0x7ff62f382d4c]
+	(No symbol) [0x0x7ff62f3d6017]
+	(No symbol) [0x0x7ff62f3aaccf]
+	(No symbol) [0x0x7ff62f3d2e24]
+	(No symbol) [0x0x7ff62f3aaa63]
+	(No symbol) [0x0x7ff62f373c91]
+	(No symbol) [0x0x7ff62f374a23]
+	GetHandleVerifier [0x0x7ff62f852ced+2979917]
+	GetHandleVerifier [0x0x7ff62f84d0f3+2956371]
+	GetHandleVerifier [0x0x7ff62f86acbd+3078173]
+	GetHandleVerifier [0x0x7ff62f5a836e+184014]
+	GetHandleVerifier [0x0x7ff62f5b024f+216495]
+	GetHandleVerifier [0x0x7ff62f5970c4+113700]
+	GetHandleVerifier [0x0x7ff62f597279+114137]
+	GetHandleVerifier [0x0x7ff62f57df78+10968]
+	BaseThreadInitThunk [0x0x7ffd0f98e8d7+23]
+	RtlUserThreadStart [0x0x7ffd11a3c34c+44]
 </t>
         </is>
       </c>
@@ -2624,27 +2624,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.139); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7defd78d5+2802741]
-	GetHandleVerifier [0x0x7ff7ded3eb70+79568]
-	(No symbol) [0x0x7ff7deadc0fa]
-	(No symbol) [0x0x7ff7deb32a96]
-	(No symbol) [0x0x7ff7deb32d4c]
-	(No symbol) [0x0x7ff7deb86017]
-	(No symbol) [0x0x7ff7deb5accf]
-	(No symbol) [0x0x7ff7deb82e24]
-	(No symbol) [0x0x7ff7deb5aa63]
-	(No symbol) [0x0x7ff7deb23c91]
-	(No symbol) [0x0x7ff7deb24a23]
-	GetHandleVerifier [0x0x7ff7df002ced+2979917]
-	GetHandleVerifier [0x0x7ff7deffd0f3+2956371]
-	GetHandleVerifier [0x0x7ff7df01acbd+3078173]
-	GetHandleVerifier [0x0x7ff7ded5836e+184014]
-	GetHandleVerifier [0x0x7ff7ded6024f+216495]
-	GetHandleVerifier [0x0x7ff7ded470c4+113700]
-	GetHandleVerifier [0x0x7ff7ded47279+114137]
-	GetHandleVerifier [0x0x7ff7ded2df78+10968]
-	BaseThreadInitThunk [0x0x7fffa28de8d7+23]
-	RtlUserThreadStart [0x0x7fffa3edc34c+44]
+	GetHandleVerifier [0x0x7ff62f8278d5+2802741]
+	GetHandleVerifier [0x0x7ff62f58eb70+79568]
+	(No symbol) [0x0x7ff62f32c0fa]
+	(No symbol) [0x0x7ff62f382a96]
+	(No symbol) [0x0x7ff62f382d4c]
+	(No symbol) [0x0x7ff62f3d6017]
+	(No symbol) [0x0x7ff62f3aaccf]
+	(No symbol) [0x0x7ff62f3d2e24]
+	(No symbol) [0x0x7ff62f3aaa63]
+	(No symbol) [0x0x7ff62f373c91]
+	(No symbol) [0x0x7ff62f374a23]
+	GetHandleVerifier [0x0x7ff62f852ced+2979917]
+	GetHandleVerifier [0x0x7ff62f84d0f3+2956371]
+	GetHandleVerifier [0x0x7ff62f86acbd+3078173]
+	GetHandleVerifier [0x0x7ff62f5a836e+184014]
+	GetHandleVerifier [0x0x7ff62f5b024f+216495]
+	GetHandleVerifier [0x0x7ff62f5970c4+113700]
+	GetHandleVerifier [0x0x7ff62f597279+114137]
+	GetHandleVerifier [0x0x7ff62f57df78+10968]
+	BaseThreadInitThunk [0x0x7ffd0f98e8d7+23]
+	RtlUserThreadStart [0x0x7ffd11a3c34c+44]
 </t>
         </is>
       </c>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>£40.00</t>
+          <t>Error: 'NoneType' object has no attribute 'find'</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2745,27 +2745,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.139); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7defd78d5+2802741]
-	GetHandleVerifier [0x0x7ff7ded3eb70+79568]
-	(No symbol) [0x0x7ff7deadc0fa]
-	(No symbol) [0x0x7ff7deb32a96]
-	(No symbol) [0x0x7ff7deb32d4c]
-	(No symbol) [0x0x7ff7deb86017]
-	(No symbol) [0x0x7ff7deb5accf]
-	(No symbol) [0x0x7ff7deb82e24]
-	(No symbol) [0x0x7ff7deb5aa63]
-	(No symbol) [0x0x7ff7deb23c91]
-	(No symbol) [0x0x7ff7deb24a23]
-	GetHandleVerifier [0x0x7ff7df002ced+2979917]
-	GetHandleVerifier [0x0x7ff7deffd0f3+2956371]
-	GetHandleVerifier [0x0x7ff7df01acbd+3078173]
-	GetHandleVerifier [0x0x7ff7ded5836e+184014]
-	GetHandleVerifier [0x0x7ff7ded6024f+216495]
-	GetHandleVerifier [0x0x7ff7ded470c4+113700]
-	GetHandleVerifier [0x0x7ff7ded47279+114137]
-	GetHandleVerifier [0x0x7ff7ded2df78+10968]
-	BaseThreadInitThunk [0x0x7fffa28de8d7+23]
-	RtlUserThreadStart [0x0x7fffa3edc34c+44]
+	GetHandleVerifier [0x0x7ff62f8278d5+2802741]
+	GetHandleVerifier [0x0x7ff62f58eb70+79568]
+	(No symbol) [0x0x7ff62f32c0fa]
+	(No symbol) [0x0x7ff62f382a96]
+	(No symbol) [0x0x7ff62f382d4c]
+	(No symbol) [0x0x7ff62f3d6017]
+	(No symbol) [0x0x7ff62f3aaccf]
+	(No symbol) [0x0x7ff62f3d2e24]
+	(No symbol) [0x0x7ff62f3aaa63]
+	(No symbol) [0x0x7ff62f373c91]
+	(No symbol) [0x0x7ff62f374a23]
+	GetHandleVerifier [0x0x7ff62f852ced+2979917]
+	GetHandleVerifier [0x0x7ff62f84d0f3+2956371]
+	GetHandleVerifier [0x0x7ff62f86acbd+3078173]
+	GetHandleVerifier [0x0x7ff62f5a836e+184014]
+	GetHandleVerifier [0x0x7ff62f5b024f+216495]
+	GetHandleVerifier [0x0x7ff62f5970c4+113700]
+	GetHandleVerifier [0x0x7ff62f597279+114137]
+	GetHandleVerifier [0x0x7ff62f57df78+10968]
+	BaseThreadInitThunk [0x0x7ffd0f98e8d7+23]
+	RtlUserThreadStart [0x0x7ffd11a3c34c+44]
 </t>
         </is>
       </c>
@@ -2843,7 +2843,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>£46.00</t>
+          <t>Error: 'NoneType' object has no attribute 'find'</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2866,27 +2866,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.139); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7defd78d5+2802741]
-	GetHandleVerifier [0x0x7ff7ded3eb70+79568]
-	(No symbol) [0x0x7ff7deadc0fa]
-	(No symbol) [0x0x7ff7deb32a96]
-	(No symbol) [0x0x7ff7deb32d4c]
-	(No symbol) [0x0x7ff7deb86017]
-	(No symbol) [0x0x7ff7deb5accf]
-	(No symbol) [0x0x7ff7deb82e24]
-	(No symbol) [0x0x7ff7deb5aa63]
-	(No symbol) [0x0x7ff7deb23c91]
-	(No symbol) [0x0x7ff7deb24a23]
-	GetHandleVerifier [0x0x7ff7df002ced+2979917]
-	GetHandleVerifier [0x0x7ff7deffd0f3+2956371]
-	GetHandleVerifier [0x0x7ff7df01acbd+3078173]
-	GetHandleVerifier [0x0x7ff7ded5836e+184014]
-	GetHandleVerifier [0x0x7ff7ded6024f+216495]
-	GetHandleVerifier [0x0x7ff7ded470c4+113700]
-	GetHandleVerifier [0x0x7ff7ded47279+114137]
-	GetHandleVerifier [0x0x7ff7ded2df78+10968]
-	BaseThreadInitThunk [0x0x7fffa28de8d7+23]
-	RtlUserThreadStart [0x0x7fffa3edc34c+44]
+	GetHandleVerifier [0x0x7ff62f8278d5+2802741]
+	GetHandleVerifier [0x0x7ff62f58eb70+79568]
+	(No symbol) [0x0x7ff62f32c0fa]
+	(No symbol) [0x0x7ff62f382a96]
+	(No symbol) [0x0x7ff62f382d4c]
+	(No symbol) [0x0x7ff62f3d6017]
+	(No symbol) [0x0x7ff62f3aaccf]
+	(No symbol) [0x0x7ff62f3d2e24]
+	(No symbol) [0x0x7ff62f3aaa63]
+	(No symbol) [0x0x7ff62f373c91]
+	(No symbol) [0x0x7ff62f374a23]
+	GetHandleVerifier [0x0x7ff62f852ced+2979917]
+	GetHandleVerifier [0x0x7ff62f84d0f3+2956371]
+	GetHandleVerifier [0x0x7ff62f86acbd+3078173]
+	GetHandleVerifier [0x0x7ff62f5a836e+184014]
+	GetHandleVerifier [0x0x7ff62f5b024f+216495]
+	GetHandleVerifier [0x0x7ff62f5970c4+113700]
+	GetHandleVerifier [0x0x7ff62f597279+114137]
+	GetHandleVerifier [0x0x7ff62f57df78+10968]
+	BaseThreadInitThunk [0x0x7ffd0f98e8d7+23]
+	RtlUserThreadStart [0x0x7ffd11a3c34c+44]
 </t>
         </is>
       </c>
@@ -2964,7 +2964,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>£53.33</t>
+          <t>Error: 'NoneType' object has no attribute 'find'</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2987,27 +2987,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.139); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7defd78d5+2802741]
-	GetHandleVerifier [0x0x7ff7ded3eb70+79568]
-	(No symbol) [0x0x7ff7deadc0fa]
-	(No symbol) [0x0x7ff7deb32a96]
-	(No symbol) [0x0x7ff7deb32d4c]
-	(No symbol) [0x0x7ff7deb86017]
-	(No symbol) [0x0x7ff7deb5accf]
-	(No symbol) [0x0x7ff7deb82e24]
-	(No symbol) [0x0x7ff7deb5aa63]
-	(No symbol) [0x0x7ff7deb23c91]
-	(No symbol) [0x0x7ff7deb24a23]
-	GetHandleVerifier [0x0x7ff7df002ced+2979917]
-	GetHandleVerifier [0x0x7ff7deffd0f3+2956371]
-	GetHandleVerifier [0x0x7ff7df01acbd+3078173]
-	GetHandleVerifier [0x0x7ff7ded5836e+184014]
-	GetHandleVerifier [0x0x7ff7ded6024f+216495]
-	GetHandleVerifier [0x0x7ff7ded470c4+113700]
-	GetHandleVerifier [0x0x7ff7ded47279+114137]
-	GetHandleVerifier [0x0x7ff7ded2df78+10968]
-	BaseThreadInitThunk [0x0x7fffa28de8d7+23]
-	RtlUserThreadStart [0x0x7fffa3edc34c+44]
+	GetHandleVerifier [0x0x7ff62f8278d5+2802741]
+	GetHandleVerifier [0x0x7ff62f58eb70+79568]
+	(No symbol) [0x0x7ff62f32c0fa]
+	(No symbol) [0x0x7ff62f382a96]
+	(No symbol) [0x0x7ff62f382d4c]
+	(No symbol) [0x0x7ff62f3d6017]
+	(No symbol) [0x0x7ff62f3aaccf]
+	(No symbol) [0x0x7ff62f3d2e24]
+	(No symbol) [0x0x7ff62f3aaa63]
+	(No symbol) [0x0x7ff62f373c91]
+	(No symbol) [0x0x7ff62f374a23]
+	GetHandleVerifier [0x0x7ff62f852ced+2979917]
+	GetHandleVerifier [0x0x7ff62f84d0f3+2956371]
+	GetHandleVerifier [0x0x7ff62f86acbd+3078173]
+	GetHandleVerifier [0x0x7ff62f5a836e+184014]
+	GetHandleVerifier [0x0x7ff62f5b024f+216495]
+	GetHandleVerifier [0x0x7ff62f5970c4+113700]
+	GetHandleVerifier [0x0x7ff62f597279+114137]
+	GetHandleVerifier [0x0x7ff62f57df78+10968]
+	BaseThreadInitThunk [0x0x7ffd0f98e8d7+23]
+	RtlUserThreadStart [0x0x7ffd11a3c34c+44]
 </t>
         </is>
       </c>
@@ -3108,27 +3108,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.139); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7defd78d5+2802741]
-	GetHandleVerifier [0x0x7ff7ded3eb70+79568]
-	(No symbol) [0x0x7ff7deadc0fa]
-	(No symbol) [0x0x7ff7deb32a96]
-	(No symbol) [0x0x7ff7deb32d4c]
-	(No symbol) [0x0x7ff7deb86017]
-	(No symbol) [0x0x7ff7deb5accf]
-	(No symbol) [0x0x7ff7deb82e24]
-	(No symbol) [0x0x7ff7deb5aa63]
-	(No symbol) [0x0x7ff7deb23c91]
-	(No symbol) [0x0x7ff7deb24a23]
-	GetHandleVerifier [0x0x7ff7df002ced+2979917]
-	GetHandleVerifier [0x0x7ff7deffd0f3+2956371]
-	GetHandleVerifier [0x0x7ff7df01acbd+3078173]
-	GetHandleVerifier [0x0x7ff7ded5836e+184014]
-	GetHandleVerifier [0x0x7ff7ded6024f+216495]
-	GetHandleVerifier [0x0x7ff7ded470c4+113700]
-	GetHandleVerifier [0x0x7ff7ded47279+114137]
-	GetHandleVerifier [0x0x7ff7ded2df78+10968]
-	BaseThreadInitThunk [0x0x7fffa28de8d7+23]
-	RtlUserThreadStart [0x0x7fffa3edc34c+44]
+	GetHandleVerifier [0x0x7ff62f8278d5+2802741]
+	GetHandleVerifier [0x0x7ff62f58eb70+79568]
+	(No symbol) [0x0x7ff62f32c0fa]
+	(No symbol) [0x0x7ff62f382a96]
+	(No symbol) [0x0x7ff62f382d4c]
+	(No symbol) [0x0x7ff62f3d6017]
+	(No symbol) [0x0x7ff62f3aaccf]
+	(No symbol) [0x0x7ff62f3d2e24]
+	(No symbol) [0x0x7ff62f3aaa63]
+	(No symbol) [0x0x7ff62f373c91]
+	(No symbol) [0x0x7ff62f374a23]
+	GetHandleVerifier [0x0x7ff62f852ced+2979917]
+	GetHandleVerifier [0x0x7ff62f84d0f3+2956371]
+	GetHandleVerifier [0x0x7ff62f86acbd+3078173]
+	GetHandleVerifier [0x0x7ff62f5a836e+184014]
+	GetHandleVerifier [0x0x7ff62f5b024f+216495]
+	GetHandleVerifier [0x0x7ff62f5970c4+113700]
+	GetHandleVerifier [0x0x7ff62f597279+114137]
+	GetHandleVerifier [0x0x7ff62f57df78+10968]
+	BaseThreadInitThunk [0x0x7ffd0f98e8d7+23]
+	RtlUserThreadStart [0x0x7ffd11a3c34c+44]
 </t>
         </is>
       </c>
@@ -3229,27 +3229,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.139); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7defd78d5+2802741]
-	GetHandleVerifier [0x0x7ff7ded3eb70+79568]
-	(No symbol) [0x0x7ff7deadc0fa]
-	(No symbol) [0x0x7ff7deb32a96]
-	(No symbol) [0x0x7ff7deb32d4c]
-	(No symbol) [0x0x7ff7deb86017]
-	(No symbol) [0x0x7ff7deb5accf]
-	(No symbol) [0x0x7ff7deb82e24]
-	(No symbol) [0x0x7ff7deb5aa63]
-	(No symbol) [0x0x7ff7deb23c91]
-	(No symbol) [0x0x7ff7deb24a23]
-	GetHandleVerifier [0x0x7ff7df002ced+2979917]
-	GetHandleVerifier [0x0x7ff7deffd0f3+2956371]
-	GetHandleVerifier [0x0x7ff7df01acbd+3078173]
-	GetHandleVerifier [0x0x7ff7ded5836e+184014]
-	GetHandleVerifier [0x0x7ff7ded6024f+216495]
-	GetHandleVerifier [0x0x7ff7ded470c4+113700]
-	GetHandleVerifier [0x0x7ff7ded47279+114137]
-	GetHandleVerifier [0x0x7ff7ded2df78+10968]
-	BaseThreadInitThunk [0x0x7fffa28de8d7+23]
-	RtlUserThreadStart [0x0x7fffa3edc34c+44]
+	GetHandleVerifier [0x0x7ff62f8278d5+2802741]
+	GetHandleVerifier [0x0x7ff62f58eb70+79568]
+	(No symbol) [0x0x7ff62f32c0fa]
+	(No symbol) [0x0x7ff62f382a96]
+	(No symbol) [0x0x7ff62f382d4c]
+	(No symbol) [0x0x7ff62f3d6017]
+	(No symbol) [0x0x7ff62f3aaccf]
+	(No symbol) [0x0x7ff62f3d2e24]
+	(No symbol) [0x0x7ff62f3aaa63]
+	(No symbol) [0x0x7ff62f373c91]
+	(No symbol) [0x0x7ff62f374a23]
+	GetHandleVerifier [0x0x7ff62f852ced+2979917]
+	GetHandleVerifier [0x0x7ff62f84d0f3+2956371]
+	GetHandleVerifier [0x0x7ff62f86acbd+3078173]
+	GetHandleVerifier [0x0x7ff62f5a836e+184014]
+	GetHandleVerifier [0x0x7ff62f5b024f+216495]
+	GetHandleVerifier [0x0x7ff62f5970c4+113700]
+	GetHandleVerifier [0x0x7ff62f597279+114137]
+	GetHandleVerifier [0x0x7ff62f57df78+10968]
+	BaseThreadInitThunk [0x0x7ffd0f98e8d7+23]
+	RtlUserThreadStart [0x0x7ffd11a3c34c+44]
 </t>
         </is>
       </c>
@@ -3350,27 +3350,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.139); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7defd78d5+2802741]
-	GetHandleVerifier [0x0x7ff7ded3eb70+79568]
-	(No symbol) [0x0x7ff7deadc0fa]
-	(No symbol) [0x0x7ff7deb32a96]
-	(No symbol) [0x0x7ff7deb32d4c]
-	(No symbol) [0x0x7ff7deb86017]
-	(No symbol) [0x0x7ff7deb5accf]
-	(No symbol) [0x0x7ff7deb82e24]
-	(No symbol) [0x0x7ff7deb5aa63]
-	(No symbol) [0x0x7ff7deb23c91]
-	(No symbol) [0x0x7ff7deb24a23]
-	GetHandleVerifier [0x0x7ff7df002ced+2979917]
-	GetHandleVerifier [0x0x7ff7deffd0f3+2956371]
-	GetHandleVerifier [0x0x7ff7df01acbd+3078173]
-	GetHandleVerifier [0x0x7ff7ded5836e+184014]
-	GetHandleVerifier [0x0x7ff7ded6024f+216495]
-	GetHandleVerifier [0x0x7ff7ded470c4+113700]
-	GetHandleVerifier [0x0x7ff7ded47279+114137]
-	GetHandleVerifier [0x0x7ff7ded2df78+10968]
-	BaseThreadInitThunk [0x0x7fffa28de8d7+23]
-	RtlUserThreadStart [0x0x7fffa3edc34c+44]
+	GetHandleVerifier [0x0x7ff62f8278d5+2802741]
+	GetHandleVerifier [0x0x7ff62f58eb70+79568]
+	(No symbol) [0x0x7ff62f32c0fa]
+	(No symbol) [0x0x7ff62f382a96]
+	(No symbol) [0x0x7ff62f382d4c]
+	(No symbol) [0x0x7ff62f3d6017]
+	(No symbol) [0x0x7ff62f3aaccf]
+	(No symbol) [0x0x7ff62f3d2e24]
+	(No symbol) [0x0x7ff62f3aaa63]
+	(No symbol) [0x0x7ff62f373c91]
+	(No symbol) [0x0x7ff62f374a23]
+	GetHandleVerifier [0x0x7ff62f852ced+2979917]
+	GetHandleVerifier [0x0x7ff62f84d0f3+2956371]
+	GetHandleVerifier [0x0x7ff62f86acbd+3078173]
+	GetHandleVerifier [0x0x7ff62f5a836e+184014]
+	GetHandleVerifier [0x0x7ff62f5b024f+216495]
+	GetHandleVerifier [0x0x7ff62f5970c4+113700]
+	GetHandleVerifier [0x0x7ff62f597279+114137]
+	GetHandleVerifier [0x0x7ff62f57df78+10968]
+	BaseThreadInitThunk [0x0x7ffd0f98e8d7+23]
+	RtlUserThreadStart [0x0x7ffd11a3c34c+44]
 </t>
         </is>
       </c>
@@ -3471,27 +3471,27 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.139); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7defd78d5+2802741]
-	GetHandleVerifier [0x0x7ff7ded3eb70+79568]
-	(No symbol) [0x0x7ff7deadc0fa]
-	(No symbol) [0x0x7ff7deb32a96]
-	(No symbol) [0x0x7ff7deb32d4c]
-	(No symbol) [0x0x7ff7deb86017]
-	(No symbol) [0x0x7ff7deb5accf]
-	(No symbol) [0x0x7ff7deb82e24]
-	(No symbol) [0x0x7ff7deb5aa63]
-	(No symbol) [0x0x7ff7deb23c91]
-	(No symbol) [0x0x7ff7deb24a23]
-	GetHandleVerifier [0x0x7ff7df002ced+2979917]
-	GetHandleVerifier [0x0x7ff7deffd0f3+2956371]
-	GetHandleVerifier [0x0x7ff7df01acbd+3078173]
-	GetHandleVerifier [0x0x7ff7ded5836e+184014]
-	GetHandleVerifier [0x0x7ff7ded6024f+216495]
-	GetHandleVerifier [0x0x7ff7ded470c4+113700]
-	GetHandleVerifier [0x0x7ff7ded47279+114137]
-	GetHandleVerifier [0x0x7ff7ded2df78+10968]
-	BaseThreadInitThunk [0x0x7fffa28de8d7+23]
-	RtlUserThreadStart [0x0x7fffa3edc34c+44]
+	GetHandleVerifier [0x0x7ff62f8278d5+2802741]
+	GetHandleVerifier [0x0x7ff62f58eb70+79568]
+	(No symbol) [0x0x7ff62f32c0fa]
+	(No symbol) [0x0x7ff62f382a96]
+	(No symbol) [0x0x7ff62f382d4c]
+	(No symbol) [0x0x7ff62f3d6017]
+	(No symbol) [0x0x7ff62f3aaccf]
+	(No symbol) [0x0x7ff62f3d2e24]
+	(No symbol) [0x0x7ff62f3aaa63]
+	(No symbol) [0x0x7ff62f373c91]
+	(No symbol) [0x0x7ff62f374a23]
+	GetHandleVerifier [0x0x7ff62f852ced+2979917]
+	GetHandleVerifier [0x0x7ff62f84d0f3+2956371]
+	GetHandleVerifier [0x0x7ff62f86acbd+3078173]
+	GetHandleVerifier [0x0x7ff62f5a836e+184014]
+	GetHandleVerifier [0x0x7ff62f5b024f+216495]
+	GetHandleVerifier [0x0x7ff62f5970c4+113700]
+	GetHandleVerifier [0x0x7ff62f597279+114137]
+	GetHandleVerifier [0x0x7ff62f57df78+10968]
+	BaseThreadInitThunk [0x0x7ffd0f98e8d7+23]
+	RtlUserThreadStart [0x0x7ffd11a3c34c+44]
 </t>
         </is>
       </c>
